--- a/apps/archetest/docs/question-review/question-review-adhd.xlsx
+++ b/apps/archetest/docs/question-review/question-review-adhd.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Инструкция" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Вопросы" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вопросы" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Вопросы'!$A$1:$K$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Вопросы'!$A$1:$K$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -44,7 +44,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -54,11 +54,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002F5496"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -100,9 +95,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -470,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A40"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -479,252 +471,84 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Ревью вопросов Архетеста — СДВГ-скрининг: 14 вопросов, две шкалы (INA 7 + HYI 7)</t>
+          <t>Авторские вопросы Archetest — редакция v2, 2026-10-16</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Проведено внутреннее содержательное ревью Codex; это не заключение комиссии психологов.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Этих вопросов ЕЩЁ НЕТ в тесте — ваши вердикты решают, попадут ли они туда. Срока нет.</t>
+          <t>Отчёт: prepared-batches-review-2026-10-16.md и JSON с исходниками, ключами и замечаниями.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Пакеты включены в рабочий банк для пилота. Интервью и эмпирическая валидация не проведены.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Зачем:</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Период: последние шесть месяцев; варианты: никогда / редко / часто / почти каждый раз.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Пользователи и психологи спрашивают, «видно ли СДВГ». Сейчас — нет: в 22 шкалах ядра конструкта</t>
+          <t>Нет подходящих ситуаций или трудно ответить — пропуск, а не нулевой балл.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>внимания и гиперактивности нет. Прототип — ASRS / ASRS-5 (WHO; Kessler 2005; Ustun 2017),</t>
+          <t>СДВГ: обычные условия с привычной поддержкой; 9 областей INA и 9 HYI; это не ASRS.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>только на уровне конструкта: пункты ASRS не переводятся и не перефразируются.</t>
+          <t>Привязанность: одни выбранные безопасные близкие отношения; без вывода о стиле.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>HON: честность–скромность, четыре фасета; не Agreeableness и не тест нравственности.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Две шкалы вместо одной:</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>HON имеет обратный ключ 3/2/1/0; остальные новые пункты — прямой 0/1/2/3.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>• INA «Невнимательность» — удержание внимания, доведение до конца, организация, забывчивость,</t>
+          <t>Стратегии помощи, вежливость, экономия и разумные границы сами по себе не дают баллов.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  потеря вещей, отвлекаемость, детали. Высокий INA при низком HYI — невнимательный тип («СДВ»).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>• HYI «Гиперактивность/импульсивность» — двигательное беспокойство, трудность ждать, перебивание,</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  импульсивные решения и реакции.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Где это будет в продукте (предложение, решение за владельцем):</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Экспериментальный блок «бета» — только психологу в кабинете. Пользователю в лучшем случае мягкая</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>рекомендация «если это мешает жить — обсудите со специалистом», никогда не «у вас СДВГ».</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Главный вопрос ревью — отличаем ли мы устойчивый паттерн от эпизода:</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Концентрация падает при депрессии, беспокойство и скачка мыслей — при гипомании, рассеянность —</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>при тревоге и недосыпе. Это эпизоды. СДВГ — давний паттерн с детства, в разных сферах жизни.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Поэтому варианты с баллом описывают «как обычно у меня», «со мной это постоянно», а не</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>«в последнее время». Скажите, где формулировка всё-таки ловит эпизод, а не черту.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>Коротко по таблице:</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>• Колонка «Шкала» показывает подкластер симптома, «Код» — INA или HYI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>• Варианты скорят ТОЛЬКО INA/HYI — ни одного балла шкалам ядра. Пустые скобки = дистрактор.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>• «Обр.» = да — балл набирается компенсаторным манёвром («пишу список — иначе половина выпадет»,</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  «прикусываю язык — иначе закончу фразу за собеседника»). Проверьте, не поймают ли такие варианты</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  просто аккуратных и собранных людей без СДВГ — оговорка «иначе…» должна это отсекать.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>• «Вердикт»: ОК / Править / Удалить. «Комментарий / правка» — формулировку можно прямо в ячейке.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>Что ещё важно:</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>1. Импульсивные реакции (обида в переписке) пересекаются с эмоциональной дисрегуляцией — это</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   спорная граница с пограничными чертами. Оставлять ли такой вопрос в HYI — ваше решение.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>2. Возраст начала (до 12 лет) ситуационным вопросом не проверить — нужен ли отдельный вопрос</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   о детстве или это за рамками самотестирования?</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>3. Язык и этика — те же критерии, что для 5.1 (INSTRUCTIONS.md). Без самообвинения: высокий балл</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   должен звучать как честное описание, а не «ленюсь».</t>
+          <t>Следующий этап: реальные когнитивные интервью и проверка измерительных свойств.</t>
         </is>
       </c>
     </row>
@@ -739,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -818,7 +642,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Удержание внимания</t>
+          <t>Внимание к деталям</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -829,35 +653,43 @@
       <c r="D2" s="4" t="inlineStr"/>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Коллега пятнадцать минут объясняет по телефону, как оформить документы, — скучно, но важно.</t>
+          <t>За последние шесть месяцев как часто в обычных условиях, с привычной помощью и лечением, если они есть, в знакомых повседневных заданиях вы пропускаете важную деталь, хотя знаете, как выполнить задание? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Где-то на середине ловлю себя на том, что думаю о своём, и прошу повторить
+          <t>Никогда или почти никогда
+[]</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Редко
+[INA 1]</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[INA 2]</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [INA 3]</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Слушаю и параллельно записываю ключевые шаги
-[]</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>Прошу прислать то же самое письмом — так надёжнее
-[INA 1]</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>Дослушиваю и задаю пару уточняющих вопросов
-[]</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr"/>
-      <c r="K2" s="4" t="inlineStr"/>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -865,7 +697,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Доведение до конца</t>
+          <t>Удержание внимания</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -876,35 +708,43 @@
       <c r="D3" s="4" t="inlineStr"/>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Дома копятся незаконченные дела: полусобранная полка, начатый онлайн-курс, одна переклеенная стена. Как обычно складываются такие проекты у вас?</t>
+          <t>За последние шесть месяцев как часто в обычных условиях, с привычной помощью и лечением, если они есть, во время необходимого, но однообразного дела ваше внимание уходит от задачи? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Если начал(а), довожу — пусть медленно
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Начинаю с азартом, но как только становится рутинно — бросаю ради нового
+          <t>Редко
+[INA 1]</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[INA 2]</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [INA 3]</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Незаконченного почти нет: редко берусь за то, что не успею
-[]</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Доделываю, только когда кто-то ждёт результат или горит срок
-[INA 1]</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -912,7 +752,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Организация</t>
+          <t>Слушание</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -920,42 +760,46 @@
           <t>INA</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="D4" s="4" t="inlineStr"/>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>В один день нужно оплатить квитанцию, забрать посылку, записаться к врачу и вернуть книгу в библиотеку.</t>
+          <t>За последние шесть месяцев как часто в обычных условиях, с привычной помощью и лечением, если они есть, в разговоре один на один вы обнаруживаете, что пропустили часть сказанного, хотя хотели слушать? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Держу всё в голове и спокойно успеваю
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Выстраиваю маршрут, чтобы всё было по пути
-[]</t>
+          <t>Редко
+[INA 1]</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Пишу список и ставлю напоминание на каждый пункт — без них половина точно выпадет
+          <t>Часто
+[INA 2]</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [INA 3]</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>Делаю одно-два дела, остальное как-то само переезжает на потом
-[INA 2]</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -963,7 +807,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Забывчивость</t>
+          <t>Завершение</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -974,35 +818,43 @@
       <c r="D5" s="4" t="inlineStr"/>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Друг напоминает: «Ты обещал(а) вернуть зарядку ещё на прошлой неделе».</t>
+          <t>За последние шесть месяцев как часто в обычных условиях, с привычной помощью и лечением, если они есть, вы оставляете необходимое дело незавершённым, переключившись на другое, хотя решили его закончить? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Извиняюсь: закрутился(ась), со мной такое бывает редко
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Помню, просто было неудобно заехать
-[]</t>
+          <t>Редко
+[INA 1]</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Тут же ставлю напоминание в телефон, иначе забуду снова
-[INA 1]</t>
+          <t>Часто
+[INA 2]</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Опять вылетело из головы — со мной это постоянно, хотя я правда собирался(ась)
+          <t>Почти каждый раз
 [INA 3]</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -1010,7 +862,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Потеря вещей</t>
+          <t>Организация</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -1018,42 +870,46 @@
           <t>INA</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="D6" s="4" t="inlineStr"/>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Утро, вы выходите из дома.</t>
+          <t>За последние шесть месяцев как часто в обычных условиях, с привычной помощью и лечением, если они есть, вам трудно выстроить порядок шагов в обычном деле, даже когда понятно, какой результат нужен? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Просто беру всё нужное и выхожу
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Минут десять ищу ключи или телефон — обычное утро
+          <t>Редко
+[INA 1]</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Часто
 [INA 2]</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Проверяю, выключены ли плита и утюг
-[]</t>
-        </is>
-      </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>У меня жёсткое правило: ключи, кошелёк, телефон — всегда в одном месте, иначе начинаются поиски
+          <t>Почти каждый раз
 [INA 3]</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1061,7 +917,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Отвлекаемость</t>
+          <t>Длительное умственное усилие</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1072,35 +928,43 @@
       <c r="D7" s="4" t="inlineStr"/>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Вы пишете отчёт в опенспейсе: рядом обсуждают чей-то отпуск, у кого-то звонит телефон.</t>
+          <t>За последние шесть месяцев как часто в обычных условиях, с привычной помощью и лечением, если они есть, вы откладываете посильную, но требующую длительного внимания задачу именно из-за трудности удерживать умственное усилие? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Надеваю наушники и продолжаю
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Шум мне не мешает, даже наоборот
-[]</t>
+          <t>Редко
+[INA 1]</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Каждая фраза рядом выдёргивает меня — к концу часа написано два абзаца
+          <t>Часто
+[INA 2]</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [INA 3]</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>Ухожу в переговорку потише
-[]</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1108,7 +972,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Внимание к деталям</t>
+          <t>Потеря вещей</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -1116,42 +980,46 @@
           <t>INA</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="D8" s="4" t="inlineStr"/>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Вы заполняете заявление на двадцать полей: даты, номера документов, адреса.</t>
+          <t>За последние шесть месяцев как часто в обычных условиях, с привычной помощью и лечением, если они есть, вы не можете найти нужную для текущего дела вещь, потому что не помните, куда её положили? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Перечитываю дважды: знаю, что иначе пропущу опечатку, не ту дату или вложение
+          <t>Никогда или почти никогда
+[]</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Редко
+[INA 1]</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[INA 2]</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [INA 3]</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Отправляю сразу — обычно всё в порядке
-[]</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Прошу кого-нибудь глянуть, если дело важное
-[]</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>Замечаю ошибку уже после отправки — со мной это частая история
-[INA 2]</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1159,46 +1027,54 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Двигательное беспокойство</t>
+          <t>Отвлечение</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>HYI</t>
+          <t>INA</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr"/>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Двухчасовое совещание, сидеть нужно на месте.</t>
+          <t>За последние шесть месяцев как часто в обычных условиях, с привычной помощью и лечением, если они есть, посторонний звук или движение отвлекает вас от дела, и вам трудно вернуться к нему? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Сижу спокойно, если тема интересная
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Кручу ручку, качаю ногой, выхожу «за водой» — сидеть без движения тяжело
-[HYI 3]</t>
+          <t>Редко
+[INA 1]</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Сижу, но мысленно уже на другой задаче
-[]</t>
+          <t>Часто
+[INA 2]</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Устаю, но это обычная усталость
-[]</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr"/>
+          <t>Почти каждый раз
+[INA 3]</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -1206,46 +1082,54 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Трудность ждать</t>
+          <t>Забывчивость</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>HYI</t>
+          <t>INA</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr"/>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Очередь в поликлинике движется медленно, перед вами ещё человек десять.</t>
+          <t>За последние шесть месяцев как часто в обычных условиях, с привычной помощью и лечением, если они есть, повседневная договорённость выпадает у вас из памяти, хотя вы собирались её выполнить? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Достаю книгу или телефон и жду
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Разговариваю с соседями по очереди
-[]</t>
+          <t>Редко
+[INA 1]</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Ухожу и возвращаюсь позже, когда будет меньше народу
-[HYI 1]</t>
+          <t>Часто
+[INA 2]</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Через пять минут хожу туда-сюда и выясняю, кто за кем, — ждать для меня пытка
-[HYI 3]</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr"/>
-      <c r="K10" s="4" t="inlineStr"/>
+          <t>Почти каждый раз
+[INA 3]</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -1253,7 +1137,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Перебивание</t>
+          <t>Мелкие движения</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1261,42 +1145,46 @@
           <t>HYI</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="D11" s="4" t="inlineStr"/>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Близкий человек подробно рассказывает о своём дне, а вам уже понятно, к чему идёт рассказ.</t>
+          <t>За последние шесть месяцев как часто в обычных условиях, с привычной помощью и лечением, если они есть, в спокойной обстановке вы непроизвольно двигаете ногой или перебираете что-то руками, когда нужно сидеть? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Дослушиваю — интересно, как расскажет
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Нарочно держу паузу и прикусываю язык — иначе закончу фразу за собеседника, я за собой это знаю
+          <t>Редко
+[HYI 1]</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[HYI 2]</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [HYI 3]</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Договариваю мысль сам(а), чтобы ускорить
-[HYI 2]</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>Киваю, но думаю о своём
-[]</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr"/>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -1304,7 +1192,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Импульсивные решения</t>
+          <t>Вставание</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1315,35 +1203,43 @@
       <c r="D12" s="4" t="inlineStr"/>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>В интернете попадается распродажа вещи, о которой вы раньше не думали, но выглядит здорово.</t>
+          <t>За последние шесть месяцев как часто в обычных условиях, с привычной помощью и лечением, если они есть, на недолгой встрече вы встаёте и начинаете ходить, хотя сейчас предполагается оставаться на месте? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Кладу в корзину и возвращаюсь через день-два
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Сравниваю цены на других сайтах
-[]</t>
+          <t>Редко
+[HYI 1]</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Закрываю вкладку: раз не думал(а) о ней раньше, значит, не нужна
-[]</t>
+          <t>Часто
+[HYI 2]</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Оформляю заказ за пару минут — я вообще быстро решаю, а разбираюсь потом
+          <t>Почти каждый раз
 [HYI 3]</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr"/>
-      <c r="K12" s="4" t="inlineStr"/>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1351,7 +1247,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Внутренний двигатель</t>
+          <t>Внутреннее беспокойство</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1359,42 +1255,46 @@
           <t>HYI</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="D13" s="4" t="inlineStr"/>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Впереди семь часов перелёта в кресле самолёта.</t>
+          <t>За последние шесть месяцев как часто в обычных условиях, с привычной помощью и лечением, если они есть, в обычное свободное время вы чувствуете внутреннюю потребность двигаться, даже когда спешить некуда? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>С удовольствием сплю или смотрю фильмы
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Заранее набираю занятий на все семь часов и встаю пройтись каждый час — иначе к концу полёта буду как на иголках
+          <t>Редко
+[HYI 1]</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[HYI 2]</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [HYI 3]</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>Читаю, иногда дремлю
-[]</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>Ёрзаю, то и дело встаю, листаю всё подряд — долго сидеть мне тяжело
-[HYI 2]</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="4" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1402,7 +1302,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Реплики на опережение</t>
+          <t>Тихий досуг</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1413,35 +1313,43 @@
       <c r="D14" s="4" t="inlineStr"/>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>На встрече с малознакомыми людьми разговор заходит о теме, в которой вы хорошо разбираетесь.</t>
+          <t>За последние шесть месяцев как часто в обычных условиях, с привычной помощью и лечением, если они есть, во время спокойного совместного занятия вам трудно заниматься им тихо, без постоянных разговоров или шума? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Ответ вылетает раньше, чем договорят вопрос, — потом неловко, но удержаться трудно
+          <t>Никогда или почти никогда
+[]</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Редко
+[HYI 1]</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[HYI 2]</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [HYI 3]</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>Жду паузы и тогда вступаю
-[]</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>Молчу, пока меня прямо не спросят
-[]</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>Даю понять, что хочу сказать, и жду очереди
-[]</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr"/>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1449,7 +1357,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Импульсивные реакции</t>
+          <t>Постоянная активность</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1457,48 +1365,272 @@
           <t>HYI</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="D15" s="4" t="inlineStr"/>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Пришло сообщение, которое вас задело.</t>
+          <t>За последние шесть месяцев как часто в обычных условиях, с привычной помощью и лечением, если они есть, вы продолжаете переходить от одного занятия к другому, потому что вам трудно остановиться и спокойно отдохнуть? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Спокойно пишу ответ — эмоции не мешают
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Не отвечаю вовсе
-[]</t>
+          <t>Редко
+[HYI 1]</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Отвечаю сразу, как чувствую
+          <t>Часто
 [HYI 2]</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Выжидаю хотя бы час, прежде чем отвечать, — по опыту знаю, что с первого порыва наговорю лишнего
+          <t>Почти каждый раз
 [HYI 3]</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Количество речи</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>HYI</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>За последние шесть месяцев как часто в обычных условиях, с привычной помощью и лечением, если они есть, в беседе вы говорите так много, что собеседникам трудно вставить слово, хотя вы собирались дать им высказаться? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Никогда или почти никогда
+[]</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Редко
+[HYI 1]</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[HYI 2]</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
+[HYI 3]</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Ответ до конца вопроса</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>HYI</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>За последние шесть месяцев как часто в обычных условиях, с привычной помощью и лечением, если они есть, вы отвечаете вслух до того, как собеседник закончил вопрос, хотя собирались дослушать? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Никогда или почти никогда
+[]</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Редко
+[HYI 1]</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[HYI 2]</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
+[HYI 3]</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Ожидание очереди</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>HYI</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>За последние шесть месяцев как часто в обычных условиях, с привычной помощью и лечением, если они есть, при обычном ожидании своей очереди вы начинаете действовать вне очереди, потому что трудно дождаться? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Никогда или почти никогда
+[]</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Редко
+[HYI 1]</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[HYI 2]</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
+[HYI 3]</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Вмешательство</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>HYI</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>За последние шесть месяцев как часто в обычных условиях, с привычной помощью и лечением, если они есть, вы вмешиваетесь в чужой разговор или занятие без приглашения, а затем замечаете, что помешали? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Никогда или почти никогда
+[]</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Редко
+[HYI 1]</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[HYI 2]</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
+[HYI 3]</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K15"/>
+  <autoFilter ref="A1:K19"/>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Выберите: ОК, Править или Удалить" type="list">
-      <formula1>"ОК,Править,Удалить"</formula1>
+    <dataValidation sqref="J2:J19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Выберите: ОК, Править, Удалить или Для пилота" type="list">
+      <formula1>"ОК,Править,Удалить,Для пилота"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
